--- a/mix-analyzer/mix-analyzer-tracker.xlsx
+++ b/mix-analyzer/mix-analyzer-tracker.xlsx
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>Todo</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E26" s="18" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Overlay detected BPM and key as colored sections. Different hue per key (chromatic mapping). BPM number per region. Contrasting borders at change points.</t>
+          <t>Beat grid lines drawn at BPM intervals (bar lines at 4x opacity). BPM + key text labels in waveform corners (amber BPM, mode-colored key name). REMAINING: chromatic color per-key regions (full hue mapping), contrasting borders at key-change points, time-varying key/BPM sections (requires windowed analysis).</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>Todo</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="F27" s="15" t="inlineStr">
         <is>
-          <t>12-row heatmap of pitch class energy over time. Shows key changes, chord progressions, tonal density.</t>
+          <t>Static 12-bar chromagram rendered in Analysis view: bar height = chroma magnitude, root highlighted in mode color (teal=major, purple=minor), in-scale notes dimmed. REMAINING: 12-row time-varying heatmap (chroma energy over time), showing key changes and chord progressions — requires per-frame windowed chromagram storage.</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="D61" s="19" t="inlineStr">
         <is>
-          <t>Todo</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="F61" s="15" t="inlineStr">
         <is>
-          <t>Offload FFT/LUFS/chromagram/BPM to worker. Prevents UI freeze on long files.</t>
+          <t>BPM moved to Web Worker (src/dsp/bpmWorker.js). analyze() returns bpm:null immediately; analyzeBPM(buffer) returns Promise, App.jsx patches stem state on Worker resolve. Channel data transferred zero-copy (Float32Array Transferable). FFT/LUFS/spectrum remain on main thread — acceptable at current file lengths.</t>
         </is>
       </c>
       <c r="G61" s="20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="D73" s="19" t="inlineStr">
         <is>
-          <t>Todo</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E73" s="17" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>Onset → BPM (task #6). Chromagram → Key (task #7). Windowed for changes. Colored regions + chromagram viz (tasks #21, #22).</t>
+          <t>Onset→BPM (#6, done). Chromagram→Key (#7, done). Beat grid + corner labels on waveform (#21, partial). Static chromagram viz (#22, partial). Full chromatic key regions and time-varying heatmap deferred.</t>
         </is>
       </c>
       <c r="G73" s="20" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="D90" s="19" t="inlineStr">
         <is>
-          <t>Todo</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E90" s="18" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="F90" s="9" t="inlineStr">
         <is>
-          <t>Tasks: #6, #7, #21, #22. Onset→BPM, chromagram→key. Colored regions. Chromagram viz.</t>
+          <t>Tasks #6, #7 done. Tasks #21, #22 partial — beat grid, BPM/key labels, static chromagram shipped. Full spec (chromatic regions, time-varying heatmap) deferred to later sprint.</t>
         </is>
       </c>
       <c r="G90" s="21" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="D115" s="33" t="inlineStr">
         <is>
-          <t>Todo</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Band analysers fftSize=512, wideband fftSize=4096. Stride mapping (Math.round(bufSize/bandBufSize)) used but needs visual QA — coloring may be slightly misaligned at transients.</t>
+          <t>Fixed: replaced stride-based mapping with temporal-window alignment. drawVectorscope now uses last 512 samples of wideband buffer (wbOffset=4096-512) for 1:1 index mapping with 512-sample band buffers. Both windows cover same ~11.6ms slice. Dot size bumped to 2px to compensate for 512 vs 4096 points.</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4503,6 +4503,41 @@
         </is>
       </c>
       <c r="G117" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>83</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>DSP pipeline performance (shared FFT, merged scan, in-place biquad)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>P5.1: computeStereo — hoisted 4xFloat64Array(8192) outside hop loop (eliminates 96 GC allocs/call). P5.2: analyze() — merged 4 separate full-buffer passes (peak/RMS/stereo corr/clipping) into 1 loop. P5.3: shared FFT pipeline (sharedFFT.js) — single N=8192 hop loop feeds spectrum, stereo, key; stereo derived via M/S identity (L=mid+side, R=mid-side), eliminating ~112 redundant FFTs. P5.4: computeLUFS — applyBiquadInPlace() halves kWeightFilter allocation (~80MB saved on 4-min track). All DSP math/outputs unchanged.</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
         <is>
           <t>Done</t>
         </is>

--- a/mix-analyzer/mix-analyzer-tracker.xlsx
+++ b/mix-analyzer/mix-analyzer-tracker.xlsx
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>Todo</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Route filter bank to output via GainNodes. Solo = hear only that band. Advanced diagnostic tool.</t>
+          <t>P6-C: banded output path (LOW/MID/HIGH GainNodes), mute buttons in transport, gain toggle without graph rebuild</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>Todo</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E46" s="17" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="F46" s="15" t="inlineStr">
         <is>
-          <t>Load reference track, level-match (LUFS-normalize), compare spectrum/LUFS/stereo/DR overlaid. Switch between tracks. Core mixing workflow.</t>
+          <t>P6-B: refStem state, loadReference callback, +REF button, LUFS-normalized refPoints passed to SpectrumDisplay</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>Todo</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>Drag reference WAV → overlay its spectrum curve on yours. MiniMeters flagship feature.</t>
+          <t>P6-A: refPoints prop on SpectrumDisplay, slope-compensated gold dashed overlay, auto-range includes ref data, REF legend</t>
         </is>
       </c>
       <c r="G47" s="21" t="inlineStr">

--- a/mix-analyzer/mix-analyzer-tracker.xlsx
+++ b/mix-analyzer/mix-analyzer-tracker.xlsx
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1x/2x/4x/8x zoom buttons + mouse wheel. Scroll slider. Auto-follows playhead when zoomed. Mini-map strip at waveform bottom. Seek accounts for zoom window.</t>
+          <t>Continuous scroll-wheel zoom 1x-32x (was discrete 1/2/4/8x). Cursor-anchored. RESET button + live readout. Adaptive beat subdivisions (bar/beat/8th/16th based on pixelsPerBeat). Scroll slider for panning.</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4540,6 +4540,426 @@
       <c r="G118" t="inlineStr">
         <is>
           <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>84</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Multi-BPM windowed detection + waveform labeling</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Want</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Divide track into overlapping 20s windows, run BPM autocorrelation per window, cluster into contiguous tempo segments [{startSec, endSec, bpm}]. Draw labeled vertical bands on waveform at segment boundaries. bpmWorker.js + analyze.js + drawWaveCanvas all need updating.</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>85</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Playback</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Interactive parametric EQ on spectrum (drag-to-eq)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Want</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Draggable EQ nodes on SpectrumDisplay SVG: x=frequency, y=gain (+-12dB), scroll=Q. EQ state in App.jsx. BiquadFilterNode (peaking) inserted after masterGain in playback chain. Render combined EQ frequency response curve on spectrum. Replaces LOW/MID/HIGH band mute buttons.</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>86</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Playback</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Spacebar play/pause hotkey</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Global keydown listener, stable toggleRef pattern. Guards against input/textarea/select.</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>87</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Resizable meter panels (drag handles)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Drag handles between SPEC/PHASE/VECTOR/LUFS. panelW state. Closure-based resize. Min 55px max 400px.</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>88</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Canvas redraw on resize (ResizeObserver + panelW effect)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>ResizeObserver on waveCanvasRef (rAF-deferred) for window resize. useEffect([panelW]) with rAF for panel drag. Covers paused state.</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>89</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Vectorscope centered + wide-mode top-half</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Always centered in panel. W&gt;H*1.1: anchors at bottom so only M&gt;0 half visible. Matches pro hardware scopes.</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>90</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Playback</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Scrub live meters: vectorscope + LUFS from buffer slice</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>computeScrubData returns lSlice/rSlice (512 samples) + momentaryDb. Vectorscope scrubVsData path + LUFS scrubDb path. Throttled at 16ms in onMove.</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>91</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>MetricCard responsive scaling</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Value font: clamp(12px,1.3vw,20px). Label fonts clamped. flex min-width 90-&gt;70px.</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>92</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Static Vectorscope: SVG to Canvas migration</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Replaced 5000 SVG circle elements with Canvas 2D in App.jsx. DPR-aware. useEffect([data,size]). Same visual output, no DOM elements.</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>93</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Playback</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Phase meter during scrub (software biquad per-band)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>computeScrubPhase: applyBiquad LP/BP/HP on 512-sample slice, Pearson correlation per band. drawPhaseMeter scrubPhaseData path. Same GUI as live playback.</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>94</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Core Analysis</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>BPM octave correction</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Doubles detected BPM when result &lt; 100 (fixes half-tempo on EDM tracks). Applied in both bpm.js and bpmWorker.js.</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>XSmall</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>95</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Adaptive waveform resolution on zoom</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>600 to 2400 pre-computed frames in sharedFFT.js (4x better spectral color at mid-zoom). zoom&gt;=4 triggers computeHighResFrames: raw buffer min/max/rms per pixel, spectral color from coarse waveData. ~1-4ms, not on RAF loop.</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>

--- a/mix-analyzer/mix-analyzer-tracker.xlsx
+++ b/mix-analyzer/mix-analyzer-tracker.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enhanced autocorrelation: hop=256, harmonic scoring (AC[lag]+0.5*AC[2lag]+...), octave correction fixed. Verified 144 BPM on test track.</t>
+          <t>During FFT analysis, extract per-hop 3-band energy proportions for spectral colouring. Amplitude stats (mx/mn/rms) computed in a SEPARATE pass over the raw buffer at a fixed 2400-chunk resolution so short tracks no longer get capped by numHops — visual bar widths stay uniform across songs of any length. Each chunk pulls its colour from the time-nearest FFT hop. FFT hop (N/2) unchanged, no smearing, DSP math intact.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Line + spectrograph modes combined MiniMeters-style (spectrograph scrolls in BG, live curve on top). M/S toggle works in both modes.</t>
+          <t>Line + spectrograph modes combined MiniMeters-style. M/S toggle works in both. Spectrograph scroll buffer now resamples (nearest-neighbour) into new dimensions on resize instead of clearing, so history is preserved. Inline slope control in the header: slider + typeable number input, range 0-6 dB/oct step 0.1, double-click slider resets to 3.0.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real-time M/S Lissajous from wideband L/R analysers. Multiband RGB coloring: red=Low, green=Mid, blue=High per sample.</t>
+          <t>Real-time M/S Lissajous from wideband L/R analysers. Multiband RGB coloring: red=Low, green=Mid, blue=High per sample. Dots (default) vs Pixels style toggle in Settings -&gt; Visual. Additive blending with reduced alpha (0.22) so dense clusters don't saturate. Scrub path now matches live path: computeScrubBands biquad-filters the slice into 6 per-band slices (shared with phase meter), drawVectorscope renders the same multiband dots.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Adjustable 0/3/4.5 dB/oct slope to match Pro-Q/Span convention.</t>
+          <t>Adjustable dB/oct slope to match Pro-Q/Span convention. Range 0-6 step 0.1 (was 0/3/4.5 presets). Inline slider + number input in LIVE SPECTRUM header with double-click-to-default (3.0). Also editable in Settings.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LUFS target, TP ceiling, mono crossover, vectorscope/band toggles.</t>
+          <t>LUFS target, TP ceiling, mono crossover, vectorscope/band toggles. Visual section added: Vectorscope Style (Dots / Pixels). Feedback Engine section (OFFLINE / CLOUD AI) with Anthropic API key field.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Fixed: replaced stride-based mapping with temporal-window alignment. drawVectorscope now uses last 512 samples of wideband buffer (wbOffset=4096-512) for 1:1 index mapping with 512-sample band buffers. Both windows cover same ~11.6ms slice. Dot size bumped to 2px to compensate for 512 vs 4096 points.</t>
+          <t>Fixed: replaced stride-based mapping with temporal-window alignment. drawVectorscope now uses last 512 samples of wideband buffer (wbOffset=4096-512) for 1:1 index mapping with 512-sample band buffers. Both windows cover same ~11.6ms slice. Dot size bumped to 2px to compensate for 512 vs 4096 points. Scrub path later matched to live path via computeScrubBands (shared per-band slices with phase meter).</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">

--- a/mix-analyzer/mix-analyzer-tracker.xlsx
+++ b/mix-analyzer/mix-analyzer-tracker.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>During FFT analysis, extract per-hop 3-band energy proportions for spectral colouring. Amplitude stats (mx/mn/rms) computed in a SEPARATE pass over the raw buffer at a fixed 2400-chunk resolution so short tracks no longer get capped by numHops — visual bar widths stay uniform across songs of any length. Each chunk pulls its colour from the time-nearest FFT hop. FFT hop (N/2) unchanged, no smearing, DSP math intact.</t>
+          <t>Enhanced autocorrelation: hop=256, harmonic scoring (AC[lag]+0.5*AC[2lag]+...), octave correction fixed. Verified 144 BPM on test track.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>During FFT analysis, extract per-frame energy in 3+ bands for spectral coloring. Same FFT data, just partition bins → color map per time-slice. Foundation for spectral waveform display.</t>
+          <t>During FFT analysis, extract per-hop 3-band energy proportions for spectral colouring. Amplitude stats (mx/mn/rms) computed in a SEPARATE pass over the raw buffer at a fixed 2400-chunk resolution so short tracks no longer get capped by numHops — visual bar widths stay uniform across songs of any length. Each chunk pulls its colour from the time-nearest FFT hop. FFT hop (N/2) unchanged, no smearing, DSP math intact.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">

--- a/mix-analyzer/mix-analyzer-tracker.xlsx
+++ b/mix-analyzer/mix-analyzer-tracker.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5073,6 +5073,41 @@
         </is>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>109</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Mobile support: touch drag, pinch zoom, stacked layout</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Runtime isMobile detection via matchMedia(max-width:768px) — src/hooks/useIsMobile.js. Touch handlers added PARALLEL to mouse handlers (never replacing): document-level touchmove/touchend for drag-scrub, onTouchStart on waveform container, pinch-to-zoom via two-finger gesture using shared applyZoomAtCursor helper (identical math to wheel zoom). touch-action:none on waveform container prevents native gesture conflicts. Mobile layout: meter row stacks vertically (flexDirection column), drag-resize handles hidden, panels go full-width, header/content padding tightened, UI zoom slider + CSS zoom disabled on mobile so native pinch handles page zoom. Desktop path is byte-equivalent — all mobile code gated behind isMobile conditionals or touch-only event listeners.</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mix-analyzer/mix-analyzer-tracker.xlsx
+++ b/mix-analyzer/mix-analyzer-tracker.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5108,6 +5108,41 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>110</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Waveform controls consolidated into waveform row</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Low/Mid/High band display toggles + M/S + SPECTRAL/UNIFORM moved out of the top transport bar and into the row directly above the waveform canvas (next to ZOOM controls). Applies to both mobile and desktop. Redundant "scroll to zoom · drag to scrub" hint dropped to make room. Keeps waveform-affecting controls visually adjacent to the waveform.</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mix-analyzer/mix-analyzer-tracker.xlsx
+++ b/mix-analyzer/mix-analyzer-tracker.xlsx
@@ -121,10 +121,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
-        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
-        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
-        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
+        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -156,10 +156,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
-        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
-        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
-        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
+        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G154"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3579,10 +3579,102 @@
         <v>Small</v>
       </c>
     </row>
+    <row r="151">
+      <c r="A151">
+        <v>116</v>
+      </c>
+      <c r="B151" t="str">
+        <v>UI / Phase A</v>
+      </c>
+      <c r="C151" t="str">
+        <v>Design tokens: space/radius/shadow/z/motion/type scales in theme.js</v>
+      </c>
+      <c r="D151" t="str">
+        <v>Done</v>
+      </c>
+      <c r="E151" t="str">
+        <v>High</v>
+      </c>
+      <c r="F151" t="str">
+        <v>Palette was the only designed layer. All spacing/radius/shadow/transition were ad-hoc (6/7/8 mixed radii, 2/3/4/5/6/7/8 gap mixed, 3 inline transition declarations). Added palette-invariant TOKENS merged into THEME alongside FONTS so THEME.space[3] / THEME.radius.md / THEME.motion.base are available everywhere. No behavior change; tokens ready for migration sites.</v>
+      </c>
+      <c r="G151" t="str">
+        <v>Small</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>117</v>
+      </c>
+      <c r="B152" t="str">
+        <v>UI / Phase A</v>
+      </c>
+      <c r="C152" t="str">
+        <v>UI primitive layer: Button + Panel + Toggle + Modal + Tabs under components/ui/</v>
+      </c>
+      <c r="D152" t="str">
+        <v>Done</v>
+      </c>
+      <c r="E152" t="str">
+        <v>High</v>
+      </c>
+      <c r="F152" t="str">
+        <v>12 hand-rolled button variants across App/Preferences/PlaybackWaveform (every site redefined padding/font/radius/border). Created variant-driven Button (primary/secondary/tertiary/tab/icon/danger, sm+md+icon sizes, built-in hover/active/focus-visible via injected stylesheet). Tabs composes Button + tab variant. Modal is responsive (width: min(92vw, 340px)), ESC-closes, focus-trap via aria-modal. Toggle is role=switch with animated thumb. prefers-reduced-motion respected globally.</v>
+      </c>
+      <c r="G152" t="str">
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>118</v>
+      </c>
+      <c r="B153" t="str">
+        <v>UI / Phase A</v>
+      </c>
+      <c r="C153" t="str">
+        <v>Migrate App.jsx + Preferences.jsx + PlaybackWaveform.jsx to ui/ primitives</v>
+      </c>
+      <c r="D153" t="str">
+        <v>Done</v>
+      </c>
+      <c r="E153" t="str">
+        <v>High</v>
+      </c>
+      <c r="F153" t="str">
+        <v>Zero hand-rolled &lt;button&gt; in the three top sprawl files (was 14 across them). Inline style={{}} count across the three dropped 159 → 136. Preferences modal now uses &lt;Modal&gt; primitive — auto-responsive, ESC-closes, backdrop-click-closes. View switcher uses &lt;Tabs&gt;. All buttons get consistent hover/focus/active feedback for free. Keyboard focus rings now present on every clickable.</v>
+      </c>
+      <c r="G153" t="str">
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>119</v>
+      </c>
+      <c r="B154" t="str">
+        <v>UI / Phase A</v>
+      </c>
+      <c r="C154" t="str">
+        <v>Canvas font bumps: phase panel labels, BPM indicator, LUFS readouts</v>
+      </c>
+      <c r="D154" t="str">
+        <v>Done</v>
+      </c>
+      <c r="E154" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F154" t="str">
+        <v>Phase panel LOW/MID/HIGH 7px → 10px bold, correlation 7px → 9px, L/R letters 6px → 8px. Waveform BPM + key indicator bold 8px → bold 11px, alpha 0.7 → 0.85. LUFS momentary 8px → bold 12px, short-term 7px → bold 10px, scale ticks 7px → 9px, M/ST labels 6px → 8px, target label 6px → 8px, SCRUB label 6px → 8px. Readability pass across drawers.js — no DSP math changed.</v>
+      </c>
+      <c r="G154" t="str">
+        <v>Small</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G150"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G154"/>
   </ignoredErrors>
 </worksheet>
 </file>